--- a/sources/jun_step8.xlsx
+++ b/sources/jun_step8.xlsx
@@ -6293,11 +6293,6 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="Y68" t="inlineStr">
         <is>
           <t>e1947643-5386-4b51-8120-285066c0ad8d</t>
@@ -7632,11 +7627,6 @@
       <c r="W81" t="inlineStr">
         <is>
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">

--- a/sources/jun_step8.xlsx
+++ b/sources/jun_step8.xlsx
@@ -928,6 +928,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
@@ -990,6 +995,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
@@ -1050,6 +1060,11 @@
       <c r="U9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>30e2beaa-6d7c-42d2-8397-096837f7826d</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9881,6 +9896,11 @@
           <t>mhmmmlmlmm</t>
         </is>
       </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
+        </is>
+      </c>
       <c r="Z108" t="inlineStr">
         <is>
           <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
@@ -9928,6 +9948,11 @@
           <t>mhmmmlhhlh</t>
         </is>
       </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
+        </is>
+      </c>
       <c r="Z109" t="inlineStr">
         <is>
           <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
@@ -9973,6 +9998,11 @@
       <c r="S110" t="inlineStr">
         <is>
           <t>mhmm</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>77355c32-3a7d-4d9f-8a8d-7ff03658cb77</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
